--- a/company/secretary/経理/銀行帳/三井住友銀行_銀行帳_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/銀行帳/三井住友銀行_銀行帳_第2期2026年4-8月.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00000000"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -52,6 +52,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCE7E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF0ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -130,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -141,6 +146,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -148,13 +154,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -524,17 +524,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,7 +554,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>口座：トランクNORTH支店 普通（口座番号マスク）／期間：2026年4月1日〜8月31日／口座開設：2026年6月17日</t>
+          <t>口座：トランクNORTH支店 普通（番号マスク）／期間：2026年4月1日〜8月31日／ValueDoor・Web21・SMBCアプリ明細＋勘定科目付補助簿より</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>※4/1〜6/16は口座開設前で取引なし。8/4〜8/31はWeb21通知に金額記載がない取引が中心のため『未確定・要確認』として表示。残高欄は補助簿の running 残高（6/17開始）。</t>
+          <t>※当口座は5月から取引あり（旧「6/17開設」は誤り・訂正）。4月分と、5月残2件・6月残4件・7/24の一部は資料に未取得。8月末実残は照会で¥11,973（9/2時点¥1,828）。黄=要確認。</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>残高</t>
+          <t>残高(補助簿)</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -624,1366 +624,1650 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>04/01〜06/16</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr"/>
-      <c r="C5" s="7" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr"/>
-      <c r="F5" s="7" t="inlineStr"/>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>口座開設前（取引なし）</t>
-        </is>
-      </c>
+          <t>◆ 2026年4月：資料に取引記載なし（要確認）</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>179</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>現金</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr"/>
-      <c r="E6" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ</t>
-        </is>
-      </c>
+          <t>◆ 2026年5月（アプリ明細・判明分）※残2件（入金50,000・出金差額約12,910）未取得</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>180</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>0</v>
-      </c>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr"/>
+      <c r="D7" s="8" t="inlineStr"/>
+      <c r="E7" s="9" t="inlineStr"/>
+      <c r="F7" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>W21 ﾕ)ｶｹﾊｼ</t>
+          <t>（アプリ明細・摘要非表示）振替11000001</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>181</v>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="8" t="n">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="G8" s="9" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>（アプリ明細・摘要非表示）振替11000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="8" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>（アプリ明細・摘要非表示）振替11000003</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr"/>
+      <c r="C10" s="8" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="n">
+        <v>22407</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>（アプリ明細・摘要非表示）振替29000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr"/>
+      <c r="C11" s="8" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <v>-145</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>182</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>通信費</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="8" t="n">
-        <v>430</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>-575</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>183</v>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>通信費</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="8" t="n">
-        <v>430</v>
-      </c>
-      <c r="G10" s="8" t="n">
-        <v>-1005</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>184</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>通信費</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8" t="n">
-        <v>430</v>
-      </c>
-      <c r="G11" s="8" t="n">
-        <v>-1435</v>
-      </c>
+      <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>（アプリ明細・摘要非表示）振替29000002</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>185</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-      <c r="E12" s="8" t="n">
-        <v>145</v>
-      </c>
-      <c r="F12" s="7" t="inlineStr"/>
-      <c r="G12" s="8" t="n">
-        <v>-1290</v>
-      </c>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr"/>
+      <c r="C12" s="8" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐ</t>
+          <t>（アプリ明細・摘要非表示／5月に計上）振替01000001</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
+          <t>◆ 2026年6月17日〜8月3日（勘定科目付 補助簿・伝票179〜214）※6月前半の一部は未取得</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>179</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>現金</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr"/>
+      <c r="E14" s="9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>180</v>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="n">
+        <v>100000</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>W21 ﾕ)ｶｹﾊｼ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>181</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <v>-145</v>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>182</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <v>-575</v>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>183</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="G18" s="9" t="n">
+        <v>-1005</v>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>184</v>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="n">
+        <v>430</v>
+      </c>
+      <c r="G19" s="9" t="n">
+        <v>-1435</v>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>185</v>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr"/>
+      <c r="E20" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="n">
+        <v>-1290</v>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>ﾌﾘｺﾐ</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B21" s="7" t="n">
         <v>186</v>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr"/>
-      <c r="E13" s="8" t="n">
+      <c r="D21" s="8" t="inlineStr"/>
+      <c r="E21" s="9" t="n">
         <v>50000</v>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="8" t="n">
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
         <v>48710</v>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐ</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B22" s="7" t="n">
         <v>187</v>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr"/>
-      <c r="E14" s="8" t="n">
+      <c r="D22" s="8" t="inlineStr"/>
+      <c r="E22" s="9" t="n">
         <v>500000</v>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="8" t="n">
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
         <v>548710</v>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ｾﾌﾞﾝBK05KJ</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B23" s="7" t="n">
         <v>188</v>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr"/>
-      <c r="F15" s="8" t="n">
+      <c r="D23" s="8" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="9" t="n">
         <v>330</v>
       </c>
-      <c r="G15" s="8" t="n">
+      <c r="G23" s="9" t="n">
         <v>548380</v>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>ｶ-ﾄﾞﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B24" s="7" t="n">
         <v>189</v>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="8" t="n">
+      <c r="D24" s="8" t="inlineStr"/>
+      <c r="E24" s="9" t="inlineStr"/>
+      <c r="F24" s="9" t="n">
         <v>90300</v>
       </c>
-      <c r="G16" s="8" t="n">
+      <c r="G24" s="9" t="n">
         <v>458080</v>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>W21 ﾕ)ｶｹﾊｼ</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B25" s="7" t="n">
         <v>190</v>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr"/>
-      <c r="F17" s="8" t="n">
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G17" s="8" t="n">
+      <c r="G25" s="9" t="n">
         <v>457935</v>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B26" s="7" t="n">
         <v>191</v>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>支払報酬料</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr"/>
-      <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="8" t="n">
+      <c r="D26" s="8" t="inlineStr"/>
+      <c r="E26" s="9" t="inlineStr"/>
+      <c r="F26" s="9" t="n">
         <v>149685</v>
       </c>
-      <c r="G18" s="8" t="n">
+      <c r="G26" s="9" t="n">
         <v>308250</v>
       </c>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>W21 ﾂｼﾞ ﾏｻｼ</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B27" s="7" t="n">
         <v>192</v>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C27" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr"/>
-      <c r="E19" s="7" t="inlineStr"/>
-      <c r="F19" s="8" t="n">
+      <c r="D27" s="8" t="inlineStr"/>
+      <c r="E27" s="9" t="inlineStr"/>
+      <c r="F27" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G19" s="8" t="n">
+      <c r="G27" s="9" t="n">
         <v>308105</v>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B28" s="7" t="n">
         <v>193</v>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr"/>
-      <c r="F20" s="8" t="n">
+      <c r="D28" s="8" t="inlineStr"/>
+      <c r="E28" s="9" t="inlineStr"/>
+      <c r="F28" s="9" t="n">
         <v>70000</v>
       </c>
-      <c r="G20" s="8" t="n">
+      <c r="G28" s="9" t="n">
         <v>238105</v>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>W21 ﾐﾗﾊﾟ</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B29" s="7" t="n">
         <v>194</v>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C29" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
-      <c r="F21" s="8" t="n">
+      <c r="D29" s="8" t="inlineStr"/>
+      <c r="E29" s="9" t="inlineStr"/>
+      <c r="F29" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G21" s="8" t="n">
+      <c r="G29" s="9" t="n">
         <v>237960</v>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H29" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B30" s="7" t="n">
         <v>195</v>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr"/>
-      <c r="F22" s="8" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="9" t="n">
         <v>6600</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G30" s="9" t="n">
         <v>231360</v>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H30" s="4" t="inlineStr">
         <is>
           <t>W21 ﾄﾞ)ﾄﾞｼﾞﾖｳｼﾝﾀﾞﾝﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B31" s="7" t="n">
         <v>196</v>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C31" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr"/>
-      <c r="F23" s="8" t="n">
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G23" s="8" t="n">
+      <c r="G31" s="9" t="n">
         <v>231215</v>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H31" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B32" s="7" t="n">
         <v>197</v>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>通信費</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr"/>
-      <c r="F24" s="8" t="n">
+      <c r="D32" s="8" t="inlineStr"/>
+      <c r="E32" s="9" t="inlineStr"/>
+      <c r="F32" s="9" t="n">
         <v>13120</v>
       </c>
-      <c r="G24" s="8" t="n">
+      <c r="G32" s="9" t="n">
         <v>218095</v>
       </c>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="H32" s="4" t="inlineStr">
         <is>
           <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B33" s="7" t="n">
         <v>198</v>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>仮払金</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>イトウアスカ</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr"/>
-      <c r="F25" s="8" t="n">
+      <c r="E33" s="9" t="inlineStr"/>
+      <c r="F33" s="9" t="n">
         <v>11077</v>
       </c>
-      <c r="G25" s="8" t="n">
+      <c r="G33" s="9" t="n">
         <v>207018</v>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B34" s="7" t="n">
         <v>199</v>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>仮払金</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>イトウアスカ</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="8" t="n">
+      <c r="E34" s="9" t="inlineStr"/>
+      <c r="F34" s="9" t="n">
         <v>5909</v>
       </c>
-      <c r="G26" s="8" t="n">
+      <c r="G34" s="9" t="n">
         <v>201109</v>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="H34" s="4" t="inlineStr">
         <is>
           <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B35" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>仮払金</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D35" s="8" t="inlineStr">
         <is>
           <t>イトウアスカ</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr"/>
-      <c r="F27" s="8" t="n">
+      <c r="E35" s="9" t="inlineStr"/>
+      <c r="F35" s="9" t="n">
         <v>10000</v>
       </c>
-      <c r="G27" s="8" t="n">
+      <c r="G35" s="9" t="n">
         <v>191109</v>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H35" s="4" t="inlineStr">
         <is>
           <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B36" s="7" t="n">
         <v>201</v>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>通信費</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr"/>
-      <c r="E28" s="7" t="inlineStr"/>
-      <c r="F28" s="8" t="n">
+      <c r="D36" s="8" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="9" t="n">
         <v>1960</v>
       </c>
-      <c r="G28" s="8" t="n">
+      <c r="G36" s="9" t="n">
         <v>189149</v>
       </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="H36" s="4" t="inlineStr">
         <is>
           <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B37" s="7" t="n">
         <v>202</v>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C37" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr"/>
-      <c r="E29" s="7" t="inlineStr"/>
-      <c r="F29" s="8" t="n">
+      <c r="D37" s="8" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="9" t="n">
         <v>150000</v>
       </c>
-      <c r="G29" s="8" t="n">
+      <c r="G37" s="9" t="n">
         <v>39149</v>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H37" s="4" t="inlineStr">
         <is>
           <t>W21 ｺｳﾍﾞﾁｻﾞｲｺﾞｳﾄﾞｳｼﾞ</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B38" s="7" t="n">
         <v>203</v>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="8" t="n">
+      <c r="D38" s="8" t="inlineStr"/>
+      <c r="E38" s="9" t="n">
         <v>500000</v>
       </c>
-      <c r="F30" s="7" t="inlineStr"/>
-      <c r="G30" s="8" t="n">
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="9" t="n">
         <v>539149</v>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H38" s="4" t="inlineStr">
         <is>
           <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B39" s="7" t="n">
         <v>204</v>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C39" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr"/>
-      <c r="E31" s="8" t="n">
+      <c r="D39" s="8" t="inlineStr"/>
+      <c r="E39" s="9" t="n">
         <v>500000</v>
       </c>
-      <c r="F31" s="7" t="inlineStr"/>
-      <c r="G31" s="8" t="n">
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="9" t="n">
         <v>1039149</v>
       </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="H39" s="4" t="inlineStr">
         <is>
           <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B40" s="7" t="n">
         <v>205</v>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>仮払金</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>イトウアスカ</t>
         </is>
       </c>
-      <c r="E32" s="7" t="inlineStr"/>
-      <c r="F32" s="8" t="n">
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="9" t="n">
         <v>200000</v>
       </c>
-      <c r="G32" s="8" t="n">
+      <c r="G40" s="9" t="n">
         <v>839149</v>
       </c>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="H40" s="4" t="inlineStr">
         <is>
           <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B41" s="7" t="n">
         <v>206</v>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="8" t="n">
+      <c r="D41" s="8" t="inlineStr"/>
+      <c r="E41" s="9" t="inlineStr"/>
+      <c r="F41" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G33" s="8" t="n">
+      <c r="G41" s="9" t="n">
         <v>839004</v>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H41" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B42" s="7" t="n">
         <v>207</v>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>仮払金</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>イトウアスカ</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr"/>
-      <c r="F34" s="8" t="n">
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="9" t="n">
         <v>300000</v>
       </c>
-      <c r="G34" s="8" t="n">
+      <c r="G42" s="9" t="n">
         <v>539004</v>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H42" s="4" t="inlineStr">
         <is>
           <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B43" s="7" t="n">
         <v>208</v>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C43" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr"/>
-      <c r="F35" s="8" t="n">
+      <c r="D43" s="8" t="inlineStr"/>
+      <c r="E43" s="9" t="inlineStr"/>
+      <c r="F43" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G43" s="9" t="n">
         <v>538859</v>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H43" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B44" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr"/>
-      <c r="F36" s="8" t="n">
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="9" t="n">
         <v>275000</v>
       </c>
-      <c r="G36" s="8" t="n">
+      <c r="G44" s="9" t="n">
         <v>263859</v>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H44" s="4" t="inlineStr">
         <is>
           <t>W21 ｶ.ｱﾙｹﾐｱｺﾈｸﾄ</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B45" s="7" t="n">
         <v>210</v>
       </c>
-      <c r="C37" s="7" t="inlineStr">
+      <c r="C45" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="8" t="n">
+      <c r="D45" s="8" t="inlineStr"/>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G37" s="8" t="n">
+      <c r="G45" s="9" t="n">
         <v>263714</v>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H45" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B46" s="7" t="n">
         <v>211</v>
       </c>
-      <c r="C38" s="9" t="inlineStr">
+      <c r="C46" s="10" t="inlineStr">
         <is>
           <t>未確定勘定</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr"/>
-      <c r="E38" s="7" t="inlineStr"/>
-      <c r="F38" s="8" t="n">
+      <c r="D46" s="8" t="inlineStr"/>
+      <c r="E46" s="9" t="inlineStr"/>
+      <c r="F46" s="9" t="n">
         <v>100000</v>
       </c>
-      <c r="G38" s="8" t="n">
+      <c r="G46" s="9" t="n">
         <v>163714</v>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H46" s="4" t="inlineStr">
         <is>
           <t>W21 ｶ.ｷｼﾕｳﾌﾟﾗﾂﾄﾌｵ-ﾑ</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B47" s="7" t="n">
         <v>212</v>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr"/>
-      <c r="F39" s="8" t="n">
+      <c r="D47" s="8" t="inlineStr"/>
+      <c r="E47" s="9" t="inlineStr"/>
+      <c r="F47" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G39" s="8" t="n">
+      <c r="G47" s="9" t="n">
         <v>163569</v>
       </c>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="H47" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B48" s="7" t="n">
         <v>213</v>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>仮払金</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>イトウアスカ</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr"/>
-      <c r="F40" s="8" t="n">
+      <c r="E48" s="9" t="inlineStr"/>
+      <c r="F48" s="9" t="n">
         <v>36000</v>
       </c>
-      <c r="G40" s="8" t="n">
+      <c r="G48" s="9" t="n">
         <v>127569</v>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B49" s="7" t="n">
         <v>214</v>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>支払手数料</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr"/>
-      <c r="F41" s="8" t="n">
+      <c r="D49" s="8" t="inlineStr"/>
+      <c r="E49" s="9" t="inlineStr"/>
+      <c r="F49" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G41" s="8" t="n">
+      <c r="G49" s="9" t="n">
         <v>127424</v>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr"/>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="inlineStr"/>
-      <c r="E42" s="7" t="inlineStr"/>
-      <c r="F42" s="10" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr"/>
-      <c r="H42" s="11" t="inlineStr">
-        <is>
-          <t>振込 出金（依頼人 デンシシ-ビ-ノウホウ）※金額メール未記載・Web21明細で要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr"/>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr"/>
-      <c r="E43" s="7" t="inlineStr"/>
-      <c r="F43" s="10" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr"/>
-      <c r="H43" s="11" t="inlineStr">
-        <is>
-          <t>振込 出金（土壌検査代）※金額メール未記載・Web21明細で要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr"/>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
-        </is>
-      </c>
-      <c r="D44" s="7" t="inlineStr"/>
-      <c r="E44" s="10" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
-      </c>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr"/>
-      <c r="H44" s="11" t="inlineStr">
-        <is>
-          <t>振込入金 ※金額メール未記載・Web21明細で要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr"/>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
-        </is>
-      </c>
-      <c r="D45" s="7" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr"/>
-      <c r="F45" s="10" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
-      </c>
-      <c r="G45" s="8" t="inlineStr"/>
-      <c r="H45" s="11" t="inlineStr">
-        <is>
-          <t>出金 ※金額メール未記載・Web21明細で要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr"/>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
-        </is>
-      </c>
-      <c r="D46" s="7" t="inlineStr"/>
-      <c r="E46" s="10" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
-      </c>
-      <c r="F46" s="7" t="inlineStr"/>
-      <c r="G46" s="8" t="inlineStr"/>
-      <c r="H46" s="11" t="inlineStr">
-        <is>
-          <t>振込入金 ※金額メール未記載・Web21明細で要確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr"/>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr"/>
-      <c r="E47" s="10" t="inlineStr">
-        <is>
-          <t>未記載</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr"/>
-      <c r="G47" s="8" t="n">
-        <v>11973</v>
-      </c>
-      <c r="H47" s="11" t="inlineStr">
-        <is>
-          <t>振込入金 ※Web21残高¥11,973（金額未記載・要確認）</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>【月次集計（金額判明分）】</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n"/>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n"/>
-      <c r="E49" s="2" t="n"/>
-      <c r="F49" s="2" t="n"/>
-      <c r="G49" s="2" t="n"/>
-      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
+          <t>◆ 2026年8月6日〜8月31日（Web21・SMBCアプリ明細）</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr"/>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>消耗品費?</t>
+        </is>
+      </c>
+      <c r="D51" s="8" t="inlineStr"/>
+      <c r="E51" s="9" t="inlineStr"/>
+      <c r="F51" s="9" t="n">
+        <v>570</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>W21 カ)モノタロウ ※科目要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr"/>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr"/>
+      <c r="E52" s="9" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F52" s="9" t="inlineStr"/>
+      <c r="G52" s="9" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>キャッシュカード セブンBK06UF（入金）</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr"/>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr"/>
+      <c r="E53" s="9" t="inlineStr"/>
+      <c r="F53" s="9" t="n">
+        <v>220</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>カードテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr"/>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr"/>
+      <c r="F54" s="9" t="n">
+        <v>300000</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>W21 イトウ アスカ</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr"/>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr"/>
+      <c r="E55" s="9" t="inlineStr"/>
+      <c r="F55" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>フリコミテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr"/>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>受取利息</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr"/>
+      <c r="E56" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="F56" s="9" t="inlineStr"/>
+      <c r="G56" s="9" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>普通預金利息（営業外収益）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr"/>
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>研究開発費?</t>
+        </is>
+      </c>
+      <c r="D57" s="8" t="inlineStr"/>
+      <c r="E57" s="9" t="inlineStr"/>
+      <c r="F57" s="9" t="n">
+        <v>6600</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>W21 ド)ドジョウシンダンヨウ ※7/24補助簿の6,600と重複の可能性・要確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr"/>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D58" s="8" t="inlineStr"/>
+      <c r="E58" s="9" t="inlineStr"/>
+      <c r="F58" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>フリコミテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr"/>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>雑収入</t>
+        </is>
+      </c>
+      <c r="D59" s="8" t="inlineStr"/>
+      <c r="E59" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="F59" s="9" t="inlineStr"/>
+      <c r="G59" s="9" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>SMBC フリコミ手数料キャッシュバック</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr"/>
+      <c r="C60" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D60" s="8" t="inlineStr"/>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>キャッシュカード セブンBK0Q5T（現金引出）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr"/>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D61" s="8" t="inlineStr"/>
+      <c r="E61" s="9" t="inlineStr"/>
+      <c r="F61" s="9" t="n">
+        <v>220</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>カードテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr"/>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>雑収入</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr"/>
+      <c r="E62" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="F62" s="9" t="inlineStr"/>
+      <c r="G62" s="9" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>SMBC テスウリョウ返金202607</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>【月次集計（判明分のみ）】</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n"/>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C65" s="8" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D65" s="8" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E65" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F65" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="C51" s="7" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="D51" s="7" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E66" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
+      <c r="F66" s="12" t="n">
+        <v>33412</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C67" s="8" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D67" s="8" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E67" s="12" t="n">
         <v>100000</v>
       </c>
-      <c r="F52" s="13" t="n">
-        <v>101005</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+      <c r="F67" s="12" t="n">
+        <v>102455</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="C53" s="7" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E68" s="12" t="n">
         <v>1550145</v>
       </c>
-      <c r="F53" s="13" t="n">
+      <c r="F68" s="12" t="n">
         <v>1385571</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C69" s="8" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D69" s="8" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="E54" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="13" t="n">
-        <v>36145</v>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>※8/4以降は金額未記載が中心（Web21明細で確定要）</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>※本帳は勘定科目付き補助簿(6/17〜8/3)＋8月Web21通知より作成。8月末の実残高はWeb21で¥11,973。正確な各取引額はWeb21『入出金明細照会』でご確認ください。</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n"/>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n"/>
-      <c r="E56" s="2" t="n"/>
-      <c r="F56" s="2" t="n"/>
-      <c r="G56" s="2" t="n"/>
-      <c r="H56" s="3" t="n"/>
+      <c r="E69" s="12" t="n">
+        <v>200221</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>364045</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>※5月は未取得2件・6月前半一部・7/24一部・4月分が未反映。確定にはValueDoor全明細が必要</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A56:H56"/>
+  <mergeCells count="9">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="H70"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/company/secretary/経理/銀行帳/三井住友銀行_銀行帳_第2期2026年4-8月.xlsx
+++ b/company/secretary/経理/銀行帳/三井住友銀行_銀行帳_第2期2026年4-8月.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -533,8 +533,8 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>※当口座は5月から取引あり（旧「6/17開設」は誤り・訂正）。4月分と、5月残2件・6月残4件・7/24の一部は資料に未取得。8月末実残は照会で¥11,973（9/2時点¥1,828）。黄=要確認。</t>
+          <t>※4月＝取引なし（動かしていない・確定）。5月入50,000・6月入100,000は京信からの振替入金（突合確認・資金移動）。8月末実残¥11,973（9/2時点¥1,828）。黄=要確認。</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -624,7 +624,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>◆ 2026年4月：資料に取引記載なし（要確認）</t>
+          <t>◆ 2026年4月：取引なし（口座を動かしていない・確定）</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>◆ 2026年5月（アプリ明細・判明分）※残2件（入金50,000・出金差額約12,910）未取得</t>
+          <t>◆ 2026年5月（判明分）※残＝出金差額 約12,910 が未取得</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -652,20 +652,24 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr"/>
-      <c r="C7" s="8" t="inlineStr"/>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>振替(資金移動)</t>
+        </is>
+      </c>
       <c r="D7" s="8" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="n">
-        <v>430</v>
-      </c>
+      <c r="E7" s="9" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr"/>
       <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>（アプリ明細・摘要非表示）振替11000001</t>
+          <t>京信5/1『提携ネット』出金50,000に対応する振替入金（突合確認）※アプリ明細では未表示</t>
         </is>
       </c>
     </row>
@@ -685,7 +689,7 @@
       <c r="G8" s="9" t="inlineStr"/>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>（アプリ明細・摘要非表示）振替11000002</t>
+          <t>（アプリ明細・摘要非表示）振替11000001</t>
         </is>
       </c>
     </row>
@@ -700,19 +704,19 @@
       <c r="D9" s="8" t="inlineStr"/>
       <c r="E9" s="9" t="inlineStr"/>
       <c r="F9" s="9" t="n">
-        <v>10000</v>
+        <v>430</v>
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>（アプリ明細・摘要非表示）振替11000003</t>
+          <t>（アプリ明細・摘要非表示）振替11000002</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr"/>
@@ -720,12 +724,12 @@
       <c r="D10" s="8" t="inlineStr"/>
       <c r="E10" s="9" t="inlineStr"/>
       <c r="F10" s="9" t="n">
-        <v>22407</v>
+        <v>10000</v>
       </c>
       <c r="G10" s="9" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>（アプリ明細・摘要非表示）振替29000001</t>
+          <t>（アプリ明細・摘要非表示）振替11000003</t>
         </is>
       </c>
     </row>
@@ -740,19 +744,19 @@
       <c r="D11" s="8" t="inlineStr"/>
       <c r="E11" s="9" t="inlineStr"/>
       <c r="F11" s="9" t="n">
-        <v>145</v>
+        <v>22407</v>
       </c>
       <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>（アプリ明細・摘要非表示）振替29000002</t>
+          <t>（アプリ明細・摘要非表示）振替29000001</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr"/>
@@ -760,56 +764,48 @@
       <c r="D12" s="8" t="inlineStr"/>
       <c r="E12" s="9" t="inlineStr"/>
       <c r="F12" s="9" t="n">
-        <v>1450</v>
+        <v>145</v>
       </c>
       <c r="G12" s="9" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
+          <t>（アプリ明細・摘要非表示）振替29000002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr"/>
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="n">
+        <v>1450</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
           <t>（アプリ明細・摘要非表示／5月に計上）振替01000001</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>◆ 2026年6月17日〜8月3日（勘定科目付 補助簿・伝票179〜214）※6月前半の一部は未取得</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-      <c r="G13" s="2" t="n"/>
-      <c r="H13" s="3" t="n"/>
-    </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>179</v>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>現金</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr"/>
-      <c r="E14" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="F14" s="9" t="inlineStr"/>
-      <c r="G14" s="9" t="n">
-        <v>100000</v>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ</t>
-        </is>
-      </c>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>◆ 2026年6月17日〜8月3日（勘定科目付 補助簿・伝票179〜214）</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -818,24 +814,24 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>180</v>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>179</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>現金</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="n">
+      <c r="E15" s="9" t="n">
         <v>100000</v>
       </c>
+      <c r="F15" s="9" t="inlineStr"/>
       <c r="G15" s="9" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>W21 ﾕ)ｶｹﾊｼ</t>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ（＝京信からの振替入金・資金移動／突合確認）</t>
         </is>
       </c>
     </row>
@@ -846,52 +842,52 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>181</v>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>180</v>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr"/>
       <c r="E16" s="9" t="inlineStr"/>
       <c r="F16" s="9" t="n">
-        <v>145</v>
+        <v>100000</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>-145</v>
+        <v>0</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ﾕ)ｶｹﾊｼ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr"/>
       <c r="E17" s="9" t="inlineStr"/>
       <c r="F17" s="9" t="n">
-        <v>430</v>
+        <v>145</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>-575</v>
+        <v>-145</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -902,7 +898,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
@@ -915,7 +911,7 @@
         <v>430</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>-1005</v>
+        <v>-575</v>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
@@ -926,11 +922,11 @@
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
@@ -943,7 +939,7 @@
         <v>430</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>-1435</v>
+        <v>-1005</v>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
@@ -954,39 +950,39 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>185</v>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>184</v>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>通信費</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr"/>
-      <c r="E20" s="9" t="n">
-        <v>145</v>
-      </c>
-      <c r="F20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="n">
+        <v>430</v>
+      </c>
       <c r="G20" s="9" t="n">
-        <v>-1290</v>
+        <v>-1435</v>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐ</t>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
@@ -995,11 +991,11 @@
       </c>
       <c r="D21" s="8" t="inlineStr"/>
       <c r="E21" s="9" t="n">
-        <v>50000</v>
+        <v>145</v>
       </c>
       <c r="F21" s="9" t="inlineStr"/>
       <c r="G21" s="9" t="n">
-        <v>48710</v>
+        <v>-1290</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
@@ -1014,7 +1010,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
@@ -1023,15 +1019,15 @@
       </c>
       <c r="D22" s="8" t="inlineStr"/>
       <c r="E22" s="9" t="n">
-        <v>500000</v>
+        <v>50000</v>
       </c>
       <c r="F22" s="9" t="inlineStr"/>
       <c r="G22" s="9" t="n">
-        <v>548710</v>
+        <v>48710</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ｾﾌﾞﾝBK05KJ</t>
+          <t>ﾌﾘｺﾐ</t>
         </is>
       </c>
     </row>
@@ -1042,24 +1038,24 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>188</v>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>187</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="9" t="n">
-        <v>330</v>
-      </c>
+      <c r="E23" s="9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F23" s="9" t="inlineStr"/>
       <c r="G23" s="9" t="n">
-        <v>548380</v>
+        <v>548710</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>ｶ-ﾄﾞﾃｽｳﾘﾖｳ</t>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ｾﾌﾞﾝBK05KJ</t>
         </is>
       </c>
     </row>
@@ -1070,24 +1066,24 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>189</v>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>188</v>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr"/>
       <c r="E24" s="9" t="inlineStr"/>
       <c r="F24" s="9" t="n">
-        <v>90300</v>
+        <v>330</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>458080</v>
+        <v>548380</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>W21 ﾕ)ｶｹﾊｼ</t>
+          <t>ｶ-ﾄﾞﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1098,24 +1094,24 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>190</v>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>189</v>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr"/>
       <c r="E25" s="9" t="inlineStr"/>
       <c r="F25" s="9" t="n">
-        <v>145</v>
+        <v>90300</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>457935</v>
+        <v>458080</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ﾕ)ｶｹﾊｼ</t>
         </is>
       </c>
     </row>
@@ -1126,24 +1122,24 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>支払報酬料</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr"/>
       <c r="E26" s="9" t="inlineStr"/>
       <c r="F26" s="9" t="n">
-        <v>149685</v>
+        <v>145</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>308250</v>
+        <v>457935</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>W21 ﾂｼﾞ ﾏｻｼ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1154,52 +1150,52 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>支払手数料</t>
+          <t>支払報酬料</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr"/>
       <c r="E27" s="9" t="inlineStr"/>
       <c r="F27" s="9" t="n">
-        <v>145</v>
+        <v>149685</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>308105</v>
+        <v>308250</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ﾂｼﾞ ﾏｻｼ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>193</v>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>192</v>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr"/>
       <c r="E28" s="9" t="inlineStr"/>
       <c r="F28" s="9" t="n">
-        <v>70000</v>
+        <v>145</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>238105</v>
+        <v>308105</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>W21 ﾐﾗﾊﾟ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1210,24 +1206,24 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>194</v>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>193</v>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr"/>
       <c r="E29" s="9" t="inlineStr"/>
       <c r="F29" s="9" t="n">
-        <v>145</v>
+        <v>70000</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>237960</v>
+        <v>238105</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ﾐﾗﾊﾟ</t>
         </is>
       </c>
     </row>
@@ -1238,24 +1234,24 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>195</v>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>194</v>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr"/>
       <c r="E30" s="9" t="inlineStr"/>
       <c r="F30" s="9" t="n">
-        <v>6600</v>
+        <v>145</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>231360</v>
+        <v>237960</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>W21 ﾄﾞ)ﾄﾞｼﾞﾖｳｼﾝﾀﾞﾝﾖｳ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1266,24 +1262,24 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>196</v>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>195</v>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr"/>
       <c r="E31" s="9" t="inlineStr"/>
       <c r="F31" s="9" t="n">
-        <v>145</v>
+        <v>6600</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>231215</v>
+        <v>231360</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ﾄﾞ)ﾄﾞｼﾞﾖｳｼﾝﾀﾞﾝﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1294,24 +1290,24 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>通信費</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr"/>
       <c r="E32" s="9" t="inlineStr"/>
       <c r="F32" s="9" t="n">
-        <v>13120</v>
+        <v>145</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>218095</v>
+        <v>231215</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1322,28 +1318,24 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
+          <t>通信費</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr"/>
       <c r="E33" s="9" t="inlineStr"/>
       <c r="F33" s="9" t="n">
-        <v>11077</v>
+        <v>13120</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>207018</v>
+        <v>218095</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>W21 ｲﾄｳ ｱｽｶ</t>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1346,7 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
@@ -1368,10 +1360,10 @@
       </c>
       <c r="E34" s="9" t="inlineStr"/>
       <c r="F34" s="9" t="n">
-        <v>5909</v>
+        <v>11077</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>201109</v>
+        <v>207018</v>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
@@ -1386,7 +1378,7 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
@@ -1400,10 +1392,10 @@
       </c>
       <c r="E35" s="9" t="inlineStr"/>
       <c r="F35" s="9" t="n">
-        <v>10000</v>
+        <v>5909</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>191109</v>
+        <v>201109</v>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -1414,28 +1406,32 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>通信費</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="inlineStr"/>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
       <c r="E36" s="9" t="inlineStr"/>
       <c r="F36" s="9" t="n">
-        <v>1960</v>
+        <v>10000</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>189149</v>
+        <v>191109</v>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
@@ -1446,24 +1442,24 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>202</v>
-      </c>
-      <c r="C37" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>201</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>通信費</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr"/>
       <c r="E37" s="9" t="inlineStr"/>
       <c r="F37" s="9" t="n">
-        <v>150000</v>
+        <v>1960</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>39149</v>
+        <v>189149</v>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>W21 ｺｳﾍﾞﾁｻﾞｲｺﾞｳﾄﾞｳｼﾞ</t>
+          <t>W21 ｶ) ﾌﾟﾘﾝﾄﾊﾟﾂｸ</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1470,7 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
@@ -1482,16 +1478,16 @@
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr"/>
-      <c r="E38" s="9" t="n">
-        <v>500000</v>
-      </c>
-      <c r="F38" s="9" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="9" t="n">
+        <v>150000</v>
+      </c>
       <c r="G38" s="9" t="n">
-        <v>539149</v>
+        <v>39149</v>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
+          <t>W21 ｺｳﾍﾞﾁｻﾞｲｺﾞｳﾄﾞｳｼﾞ</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1498,7 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
@@ -1515,7 +1511,7 @@
       </c>
       <c r="F39" s="9" t="inlineStr"/>
       <c r="G39" s="9" t="n">
-        <v>1039149</v>
+        <v>539149</v>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
@@ -1530,28 +1526,24 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>205</v>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
-      <c r="E40" s="9" t="inlineStr"/>
-      <c r="F40" s="9" t="n">
-        <v>200000</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
+        </is>
+      </c>
+      <c r="D40" s="8" t="inlineStr"/>
+      <c r="E40" s="9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F40" s="9" t="inlineStr"/>
       <c r="G40" s="9" t="n">
-        <v>839149</v>
+        <v>1039149</v>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>W21 ｲﾄｳ ｱｽｶ</t>
+          <t>ｷﾔﾂｼﾕｶ-ﾄﾞ ENET069730</t>
         </is>
       </c>
     </row>
@@ -1562,24 +1554,28 @@
         </is>
       </c>
       <c r="B41" s="7" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr"/>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
       <c r="E41" s="9" t="inlineStr"/>
       <c r="F41" s="9" t="n">
-        <v>145</v>
+        <v>200000</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>839004</v>
+        <v>839149</v>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
@@ -1590,28 +1586,24 @@
         </is>
       </c>
       <c r="B42" s="7" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D42" s="8" t="inlineStr"/>
       <c r="E42" s="9" t="inlineStr"/>
       <c r="F42" s="9" t="n">
-        <v>300000</v>
+        <v>145</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>539004</v>
+        <v>839004</v>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>W21 ｲﾄｳ ｱｽｶ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1622,24 +1614,28 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr"/>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
       <c r="E43" s="9" t="inlineStr"/>
       <c r="F43" s="9" t="n">
-        <v>145</v>
+        <v>300000</v>
       </c>
       <c r="G43" s="9" t="n">
-        <v>538859</v>
+        <v>539004</v>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1646,24 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>209</v>
-      </c>
-      <c r="C44" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>208</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
       <c r="E44" s="9" t="inlineStr"/>
       <c r="F44" s="9" t="n">
-        <v>275000</v>
+        <v>145</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>263859</v>
+        <v>538859</v>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>W21 ｶ.ｱﾙｹﾐｱｺﾈｸﾄ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1678,52 +1674,52 @@
         </is>
       </c>
       <c r="B45" s="7" t="n">
-        <v>210</v>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>209</v>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr"/>
       <c r="E45" s="9" t="inlineStr"/>
       <c r="F45" s="9" t="n">
-        <v>145</v>
+        <v>275000</v>
       </c>
       <c r="G45" s="9" t="n">
-        <v>263714</v>
+        <v>263859</v>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ｶ.ｱﾙｹﾐｱｺﾈｸﾄ</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>211</v>
-      </c>
-      <c r="C46" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+        <v>210</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr"/>
       <c r="E46" s="9" t="inlineStr"/>
       <c r="F46" s="9" t="n">
-        <v>100000</v>
+        <v>145</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>163714</v>
+        <v>263714</v>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>W21 ｶ.ｷｼﾕｳﾌﾟﾗﾂﾄﾌｵ-ﾑ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1734,56 +1730,52 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>212</v>
-      </c>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+        <v>211</v>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr"/>
       <c r="E47" s="9" t="inlineStr"/>
       <c r="F47" s="9" t="n">
-        <v>145</v>
+        <v>100000</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>163569</v>
+        <v>163714</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
+          <t>W21 ｶ.ｷｼﾕｳﾌﾟﾗﾂﾄﾌｵ-ﾑ</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B48" s="7" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr"/>
       <c r="E48" s="9" t="inlineStr"/>
       <c r="F48" s="9" t="n">
-        <v>36000</v>
+        <v>145</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>127569</v>
+        <v>163569</v>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>W21 ｲﾄｳ ｱｽｶ</t>
+          <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
@@ -1794,86 +1786,94 @@
         </is>
       </c>
       <c r="B49" s="7" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D49" s="8" t="inlineStr"/>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
       <c r="E49" s="9" t="inlineStr"/>
       <c r="F49" s="9" t="n">
+        <v>36000</v>
+      </c>
+      <c r="G49" s="9" t="n">
+        <v>127569</v>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>W21 ｲﾄｳ ｱｽｶ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>214</v>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr"/>
+      <c r="E50" s="9" t="inlineStr"/>
+      <c r="F50" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="G49" s="9" t="n">
+      <c r="G50" s="9" t="n">
         <v>127424</v>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>ﾌﾘｺﾐﾃｽｳﾘﾖｳ</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
         <is>
           <t>◆ 2026年8月6日〜8月31日（Web21・SMBCアプリ明細）</t>
         </is>
       </c>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="3" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr"/>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>消耗品費?</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr"/>
-      <c r="E51" s="9" t="inlineStr"/>
-      <c r="F51" s="9" t="n">
-        <v>570</v>
-      </c>
-      <c r="G51" s="9" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>W21 カ)モノタロウ ※科目要確認</t>
-        </is>
-      </c>
+      <c r="B51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n"/>
+      <c r="E51" s="2" t="n"/>
+      <c r="F51" s="2" t="n"/>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr"/>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>未確定勘定</t>
+          <t>消耗品費?</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr"/>
-      <c r="E52" s="9" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F52" s="9" t="inlineStr"/>
+      <c r="E52" s="9" t="inlineStr"/>
+      <c r="F52" s="9" t="n">
+        <v>570</v>
+      </c>
       <c r="G52" s="9" t="inlineStr"/>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>キャッシュカード セブンBK06UF（入金）</t>
+          <t>W21 カ)モノタロウ ※科目要確認</t>
         </is>
       </c>
     </row>
@@ -1884,20 +1884,20 @@
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr"/>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr"/>
-      <c r="E53" s="9" t="inlineStr"/>
-      <c r="F53" s="9" t="n">
-        <v>220</v>
-      </c>
+      <c r="E53" s="9" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F53" s="9" t="inlineStr"/>
       <c r="G53" s="9" t="inlineStr"/>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>カードテスウリョウ</t>
+          <t>キャッシュカード セブンBK06UF（入金）</t>
         </is>
       </c>
     </row>
@@ -1910,22 +1910,18 @@
       <c r="B54" s="7" t="inlineStr"/>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>仮払金</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>イトウアスカ</t>
-        </is>
-      </c>
+          <t>支払手数料</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr"/>
       <c r="E54" s="9" t="inlineStr"/>
       <c r="F54" s="9" t="n">
-        <v>300000</v>
+        <v>220</v>
       </c>
       <c r="G54" s="9" t="inlineStr"/>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>W21 イトウ アスカ</t>
+          <t>カードテスウリョウ</t>
         </is>
       </c>
     </row>
@@ -1938,66 +1934,70 @@
       <c r="B55" s="7" t="inlineStr"/>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>支払手数料</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr"/>
+          <t>仮払金</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>イトウアスカ</t>
+        </is>
+      </c>
       <c r="E55" s="9" t="inlineStr"/>
       <c r="F55" s="9" t="n">
-        <v>145</v>
+        <v>300000</v>
       </c>
       <c r="G55" s="9" t="inlineStr"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>フリコミテスウリョウ</t>
+          <t>W21 イトウ アスカ</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr"/>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>受取利息</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr"/>
-      <c r="E56" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="F56" s="9" t="inlineStr"/>
+      <c r="E56" s="9" t="inlineStr"/>
+      <c r="F56" s="9" t="n">
+        <v>145</v>
+      </c>
       <c r="G56" s="9" t="inlineStr"/>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>普通預金利息（営業外収益）</t>
+          <t>フリコミテスウリョウ</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr"/>
-      <c r="C57" s="10" t="inlineStr">
-        <is>
-          <t>研究開発費?</t>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>受取利息</t>
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr"/>
-      <c r="E57" s="9" t="inlineStr"/>
-      <c r="F57" s="9" t="n">
-        <v>6600</v>
-      </c>
+      <c r="E57" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="F57" s="9" t="inlineStr"/>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>W21 ド)ドジョウシンダンヨウ ※7/24補助簿の6,600と重複の可能性・要確認</t>
+          <t>普通預金利息（営業外収益）</t>
         </is>
       </c>
     </row>
@@ -2008,68 +2008,68 @@
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr"/>
-      <c r="C58" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>研究開発費?</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr"/>
       <c r="E58" s="9" t="inlineStr"/>
       <c r="F58" s="9" t="n">
-        <v>145</v>
+        <v>6600</v>
       </c>
       <c r="G58" s="9" t="inlineStr"/>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>フリコミテスウリョウ</t>
+          <t>W21 ド)ドジョウシンダンヨウ ※7/24分とは別取引（俊さん確認）</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr"/>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>雑収入</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr"/>
-      <c r="E59" s="9" t="n">
+      <c r="E59" s="9" t="inlineStr"/>
+      <c r="F59" s="9" t="n">
         <v>145</v>
       </c>
-      <c r="F59" s="9" t="inlineStr"/>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>SMBC フリコミ手数料キャッシュバック</t>
+          <t>フリコミテスウリョウ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr"/>
-      <c r="C60" s="10" t="inlineStr">
-        <is>
-          <t>未確定勘定</t>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>雑収入</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr"/>
-      <c r="E60" s="9" t="inlineStr"/>
-      <c r="F60" s="9" t="n">
-        <v>20000</v>
-      </c>
+      <c r="E60" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="F60" s="9" t="inlineStr"/>
       <c r="G60" s="9" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>キャッシュカード セブンBK0Q5T（現金引出）</t>
+          <t>SMBC フリコミ手数料キャッシュバック</t>
         </is>
       </c>
     </row>
@@ -2080,88 +2080,89 @@
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr"/>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>支払手数料</t>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>未確定勘定</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr"/>
       <c r="E61" s="9" t="inlineStr"/>
       <c r="F61" s="9" t="n">
-        <v>220</v>
+        <v>20000</v>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>カードテスウリョウ</t>
+          <t>キャッシュカード セブンBK0Q5T（現金引出）</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr"/>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>雑収入</t>
+          <t>支払手数料</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr"/>
-      <c r="E62" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="F62" s="9" t="inlineStr"/>
+      <c r="E62" s="9" t="inlineStr"/>
+      <c r="F62" s="9" t="n">
+        <v>220</v>
+      </c>
       <c r="G62" s="9" t="inlineStr"/>
       <c r="H62" s="4" t="inlineStr">
         <is>
+          <t>カードテスウリョウ</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr"/>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>雑収入</t>
+        </is>
+      </c>
+      <c r="D63" s="8" t="inlineStr"/>
+      <c r="E63" s="9" t="n">
+        <v>45</v>
+      </c>
+      <c r="F63" s="9" t="inlineStr"/>
+      <c r="G63" s="9" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
           <t>SMBC テスウリョウ返金202607</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>【月次集計（判明分のみ）】</t>
         </is>
       </c>
-      <c r="B64" s="2" t="n"/>
-      <c r="C64" s="2" t="n"/>
-      <c r="D64" s="2" t="n"/>
-      <c r="E64" s="2" t="n"/>
-      <c r="F64" s="2" t="n"/>
-      <c r="G64" s="2" t="n"/>
-      <c r="H64" s="3" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>入金計</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="inlineStr">
-        <is>
-          <t>出金計</t>
-        </is>
-      </c>
-      <c r="E65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="12" t="n">
-        <v>0</v>
-      </c>
+      <c r="B65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n"/>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="3" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -2178,13 +2179,13 @@
         <v>0</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>33412</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
@@ -2198,16 +2199,16 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>102455</v>
+        <v>33412</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -2221,51 +2222,81 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>1550145</v>
+        <v>100000</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>1385571</v>
+        <v>102455</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>入金計</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>出金計</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>1550145</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>1385571</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>入金計</t>
         </is>
       </c>
-      <c r="D69" s="8" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>出金計</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="E70" s="12" t="n">
         <v>200221</v>
       </c>
-      <c r="F69" s="12" t="n">
+      <c r="F70" s="12" t="n">
         <v>364045</v>
       </c>
     </row>
-    <row r="70">
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>※5月は未取得2件・6月前半一部・7/24一部・4月分が未反映。確定にはValueDoor全明細が必要</t>
-        </is>
-      </c>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>※残る未取得：5月の出金差額 約12,910／7/24の6件。4月は取引なし。5月入50,000・6月入100,000は京信振替で確認済。</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="3" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="H70"/>
+    <mergeCell ref="A65:H65"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:H6"/>
   </mergeCells>
